--- a/INSTANCES/instances_xlsx/A_MTN_5/273FL_10A_1.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/273FL_10A_1.xlsx
@@ -8943,7 +8943,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -9011,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -9079,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
